--- a/TESSERA-Rack-ATFM.xlsx
+++ b/TESSERA-Rack-ATFM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\P1350662\Downloads\TESSERA-Export\ATFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{237AE50B-DEA0-4A90-BE06-CCFAF3646394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC052E5F-8E1E-460F-ADEA-D507A07189EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="133">
   <si>
     <t>TESSERA Excel Import / Export Guide</t>
   </si>
@@ -427,6 +427,9 @@
   </si>
   <si>
     <t>LDC - p20r02</t>
+  </si>
+  <si>
+    <t>Operational</t>
   </si>
 </sst>
 </file>
@@ -1486,6 +1489,12 @@
       <c r="C2" s="5" t="s">
         <v>95</v>
       </c>
+      <c r="E2" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="P2" s="7" t="s">
         <v>96</v>
       </c>
@@ -1497,6 +1506,12 @@
       <c r="C3" s="5" t="s">
         <v>97</v>
       </c>
+      <c r="E3" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="P3" s="7" t="s">
         <v>98</v>
       </c>
@@ -1508,6 +1523,12 @@
       <c r="C4" s="5" t="s">
         <v>99</v>
       </c>
+      <c r="E4" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="P4" s="7" t="s">
         <v>100</v>
       </c>
@@ -1519,6 +1540,12 @@
       <c r="C5" s="5" t="s">
         <v>101</v>
       </c>
+      <c r="E5" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="P5" s="7" t="s">
         <v>102</v>
       </c>
@@ -1530,6 +1557,12 @@
       <c r="C6" s="5" t="s">
         <v>104</v>
       </c>
+      <c r="E6" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="P6" s="7" t="s">
         <v>103</v>
       </c>
@@ -1541,6 +1574,12 @@
       <c r="C7" s="5" t="s">
         <v>105</v>
       </c>
+      <c r="E7" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="P7" s="7" t="s">
         <v>103</v>
       </c>
@@ -1552,6 +1591,12 @@
       <c r="C8" s="5" t="s">
         <v>106</v>
       </c>
+      <c r="E8" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="P8" s="7" t="s">
         <v>103</v>
       </c>
@@ -1563,6 +1608,12 @@
       <c r="C9" s="5" t="s">
         <v>107</v>
       </c>
+      <c r="E9" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="P9" s="7" t="s">
         <v>103</v>
       </c>
@@ -1574,6 +1625,12 @@
       <c r="C10" s="5" t="s">
         <v>108</v>
       </c>
+      <c r="E10" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="P10" s="7" t="s">
         <v>103</v>
       </c>
@@ -1585,6 +1642,12 @@
       <c r="C11" s="5" t="s">
         <v>109</v>
       </c>
+      <c r="E11" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="P11" s="7" t="s">
         <v>103</v>
       </c>
@@ -1596,6 +1659,12 @@
       <c r="C12" s="5" t="s">
         <v>110</v>
       </c>
+      <c r="E12" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="P12" s="7" t="s">
         <v>103</v>
       </c>
@@ -1607,6 +1676,12 @@
       <c r="C13" s="5" t="s">
         <v>111</v>
       </c>
+      <c r="E13" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="P13" s="7" t="s">
         <v>103</v>
       </c>
@@ -1618,6 +1693,12 @@
       <c r="C14" s="5" t="s">
         <v>112</v>
       </c>
+      <c r="E14" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="P14" s="7" t="s">
         <v>103</v>
       </c>
@@ -1629,6 +1710,12 @@
       <c r="C15" s="5" t="s">
         <v>113</v>
       </c>
+      <c r="E15" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="P15" s="7" t="s">
         <v>103</v>
       </c>
@@ -1640,6 +1727,12 @@
       <c r="C16" s="5" t="s">
         <v>114</v>
       </c>
+      <c r="E16" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="P16" s="7" t="s">
         <v>103</v>
       </c>
@@ -1651,6 +1744,12 @@
       <c r="C17" s="5" t="s">
         <v>115</v>
       </c>
+      <c r="E17" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="P17" s="7" t="s">
         <v>103</v>
       </c>
@@ -1662,6 +1761,12 @@
       <c r="C18" s="5" t="s">
         <v>116</v>
       </c>
+      <c r="E18" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="P18" s="7" t="s">
         <v>103</v>
       </c>
@@ -1673,6 +1778,12 @@
       <c r="C19" s="5" t="s">
         <v>117</v>
       </c>
+      <c r="E19" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="P19" s="7" t="s">
         <v>103</v>
       </c>
@@ -1684,6 +1795,12 @@
       <c r="C20" s="5" t="s">
         <v>118</v>
       </c>
+      <c r="E20" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="P20" s="7" t="s">
         <v>103</v>
       </c>
@@ -1695,6 +1812,12 @@
       <c r="C21" s="5" t="s">
         <v>119</v>
       </c>
+      <c r="E21" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="P21" s="7" t="s">
         <v>103</v>
       </c>
@@ -1706,6 +1829,12 @@
       <c r="C22" s="5" t="s">
         <v>120</v>
       </c>
+      <c r="E22" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="P22" s="7" t="s">
         <v>103</v>
       </c>
@@ -1717,6 +1846,12 @@
       <c r="C23" s="5" t="s">
         <v>121</v>
       </c>
+      <c r="E23" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="P23" s="7" t="s">
         <v>103</v>
       </c>
@@ -1728,6 +1863,12 @@
       <c r="C24" s="5" t="s">
         <v>122</v>
       </c>
+      <c r="E24" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="P24" s="7" t="s">
         <v>103</v>
       </c>
@@ -1739,6 +1880,12 @@
       <c r="C25" s="5" t="s">
         <v>123</v>
       </c>
+      <c r="E25" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
@@ -1747,6 +1894,12 @@
       <c r="C26" s="5" t="s">
         <v>124</v>
       </c>
+      <c r="E26" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
@@ -1755,6 +1908,12 @@
       <c r="C27" s="5" t="s">
         <v>125</v>
       </c>
+      <c r="E27" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
@@ -1763,6 +1922,12 @@
       <c r="C28" s="5" t="s">
         <v>126</v>
       </c>
+      <c r="E28" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
@@ -1771,6 +1936,12 @@
       <c r="C29" s="5" t="s">
         <v>127</v>
       </c>
+      <c r="E29" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
@@ -1779,6 +1950,12 @@
       <c r="C30" s="5" t="s">
         <v>128</v>
       </c>
+      <c r="E30" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
@@ -1787,6 +1964,12 @@
       <c r="C31" s="5" t="s">
         <v>129</v>
       </c>
+      <c r="E31" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
@@ -1795,13 +1978,25 @@
       <c r="C32" s="5" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E32" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>131</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
